--- a/src/test/resources/testdataCRM/ClientsDataExcel.xlsx
+++ b/src/test/resources/testdataCRM/ClientsDataExcel.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROJECT_FRAMEWORK\AutomationFrameworkSelenium\src\test\resources\testdataCRM\"/>
     </mc:Choice>
@@ -18,7 +18,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
   </extLst>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="48">
   <si>
     <t>VAT</t>
   </si>
@@ -167,12 +167,16 @@
   </si>
   <si>
     <t>TV</t>
+  </si>
+  <si>
+    <t>pass</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -280,7 +284,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -291,6 +295,16 @@
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none">
+        <fgColor indexed="11"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="11"/>
       </patternFill>
     </fill>
   </fills>
@@ -307,7 +321,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -345,6 +359,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -663,14 +683,14 @@
   <dimension ref="A1:H3"/>
   <sheetFormatPr defaultColWidth="8.8984375" defaultRowHeight="18" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.5" style="10" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="2" max="2" width="20.09765625" style="10" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="41.19921875" style="10" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="21.5" style="10" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="23.5" style="10" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="19.796875" style="10" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="7" max="8" width="8.8984375" style="10" collapsed="1"/>
-    <col min="9" max="16384" width="8.8984375" style="1" collapsed="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="10" width="20.5" collapsed="true"/>
+    <col min="2" max="2" customWidth="true" style="10" width="20.09765625" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="10" width="41.19921875" collapsed="true"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="10" width="21.5" collapsed="true"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="10" width="23.5" collapsed="true"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="10" width="19.796875" collapsed="true"/>
+    <col min="7" max="8" style="10" width="8.8984375" collapsed="true"/>
+    <col min="9" max="16384" style="1" width="8.8984375" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -703,7 +723,9 @@
       <c r="C2" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="D2" s="13"/>
+      <c r="D2" s="16" t="s">
+        <v>47</v>
+      </c>
       <c r="E2" s="11"/>
       <c r="F2" s="11"/>
       <c r="G2" s="11"/>
@@ -740,21 +762,21 @@
   <dimension ref="A1:N4"/>
   <sheetFormatPr defaultColWidth="18.19921875" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.8984375" style="2" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="2" max="2" width="27.69921875" style="2" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="21.3984375" style="2" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="21.8984375" style="2" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="11.69921875" style="2" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="12.09765625" style="2" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="7" max="7" width="9" style="2" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="8" max="8" width="10.59765625" style="2" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="14.3984375" style="2" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="10" max="10" width="25.5" style="2" customWidth="1" collapsed="1"/>
-    <col min="11" max="11" width="4.796875" style="2" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="12" max="12" width="15.3984375" style="2" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="13" max="13" width="15.3984375" style="2" customWidth="1"/>
-    <col min="14" max="14" width="8" style="2" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="15" max="16384" width="18.19921875" style="2" collapsed="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="2" width="15.8984375" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="2" width="27.69921875" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="2" width="21.3984375" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="2" width="21.8984375" collapsed="true"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="2" width="11.69921875" collapsed="true"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="2" width="12.09765625" collapsed="true"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="2" width="9.0" collapsed="true"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="2" width="10.59765625" collapsed="true"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" style="2" width="14.3984375" collapsed="true"/>
+    <col min="10" max="10" customWidth="true" style="2" width="25.5" collapsed="true"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" style="2" width="4.796875" collapsed="true"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" style="2" width="15.3984375" collapsed="true"/>
+    <col min="13" max="13" customWidth="true" style="2" width="15.3984375"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="2" width="8.0" collapsed="true"/>
+    <col min="15" max="16384" style="2" width="18.19921875" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" s="7" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
